--- a/DEMATEL analysis and review coding/expert_responses.xlsx
+++ b/DEMATEL analysis and review coding/expert_responses.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uetpk-my.sharepoint.com/personal/adeel_munir_uet_edu_pk/Documents/Drive G/Data science coding/VSCode programming/DEMATEL analysis and review coding/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vult-my.sharepoint.com/personal/adeel_munir_evaf_vu_lt/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2FB91564-CD00-410D-B773-67EBC0407E27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3A49492-1BBE-4794-B7F8-8718DCAF61DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="E1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3825" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3825" uniqueCount="20">
   <si>
     <t>F1</t>
   </si>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>M</t>
+  </si>
+  <si>
+    <t>H</t>
   </si>
 </sst>
 </file>
@@ -558,7 +561,7 @@
         <v>16</v>
       </c>
       <c r="H3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I3" t="s">
         <v>16</v>
@@ -2325,7 +2328,7 @@
         <v>15</v>
       </c>
       <c r="I6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J6" t="s">
         <v>16</v>
@@ -2484,7 +2487,7 @@
         <v>18</v>
       </c>
       <c r="L9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M9" t="s">
         <v>16</v>
@@ -3179,7 +3182,7 @@
         <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I7" t="s">
         <v>16</v>
@@ -4746,7 +4749,7 @@
         <v>16</v>
       </c>
       <c r="I6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J6" t="s">
         <v>16</v>
@@ -5388,7 +5391,7 @@
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
         <v>16</v>
@@ -5568,7 +5571,7 @@
         <v>16</v>
       </c>
       <c r="N6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O6" t="s">
         <v>16</v>
@@ -5659,7 +5662,7 @@
         <v>16</v>
       </c>
       <c r="K8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L8" t="s">
         <v>15</v>
@@ -5818,7 +5821,7 @@
         <v>18</v>
       </c>
       <c r="N11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O11" t="s">
         <v>16</v>
@@ -5853,7 +5856,7 @@
         <v>16</v>
       </c>
       <c r="I12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J12" t="s">
         <v>16</v>
@@ -5965,7 +5968,7 @@
         <v>15</v>
       </c>
       <c r="M14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N14" t="s">
         <v>15</v>
@@ -6263,7 +6266,7 @@
         <v>16</v>
       </c>
       <c r="J4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K4" t="s">
         <v>16</v>
@@ -6551,7 +6554,7 @@
         <v>17</v>
       </c>
       <c r="F10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G10" t="s">
         <v>15</v>
@@ -9729,7 +9732,7 @@
         <v>15</v>
       </c>
       <c r="F9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G9" t="s">
         <v>16</v>
@@ -9797,7 +9800,7 @@
         <v>16</v>
       </c>
       <c r="L10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M10" t="s">
         <v>16</v>
@@ -10739,7 +10742,7 @@
         <v>16</v>
       </c>
       <c r="G13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
@@ -12256,7 +12259,7 @@
         <v>18</v>
       </c>
       <c r="H11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I11" t="s">
         <v>16</v>

--- a/DEMATEL analysis and review coding/expert_responses.xlsx
+++ b/DEMATEL analysis and review coding/expert_responses.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vult-my.sharepoint.com/personal/adeel_munir_evaf_vu_lt/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uetpk-my.sharepoint.com/personal/adeel_munir_uet_edu_pk/Documents/Drive G/Data science coding/VSCode programming/DEMATEL analysis and review coding/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3A49492-1BBE-4794-B7F8-8718DCAF61DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{F3A49492-1BBE-4794-B7F8-8718DCAF61DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DE9C826-BC84-4C55-803F-49A8180C1540}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="E1" sheetId="1" r:id="rId1"/>
@@ -1730,7 +1730,7 @@
         <v>16</v>
       </c>
       <c r="L10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M10" t="s">
         <v>15</v>
@@ -3294,7 +3294,7 @@
         <v>18</v>
       </c>
       <c r="L9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M9" t="s">
         <v>15</v>
@@ -5718,7 +5718,7 @@
         <v>16</v>
       </c>
       <c r="M9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N9" t="s">
         <v>16</v>
@@ -9838,7 +9838,7 @@
         <v>18</v>
       </c>
       <c r="H11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I11" t="s">
         <v>18</v>
@@ -11452,7 +11452,7 @@
         <v>16</v>
       </c>
       <c r="H11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I11" t="s">
         <v>16</v>
@@ -12127,7 +12127,7 @@
         <v>16</v>
       </c>
       <c r="N8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O8" t="s">
         <v>16</v>
